--- a/extenbooks/S301_extenbook.xlsx
+++ b/extenbooks/S301_extenbook.xlsx
@@ -4406,7 +4406,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5558,11 +5558,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5585,88 +5585,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Change in expenditure relative to change in income, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S301_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S301_DPR.md", "epr": "Technical/docs/series/S301_EPR.md", "loader": "Technical/code/L01_loaders/L01_S301_load.py", "processor": "Technical/code/P02_processors/P02_S301_construct.py", "validator": "Technical/code/V03_validators/V03_S301_validate.py", "processed": "Technical/data/processed/S301.parquet", "chopped_csv": "Technical/chopped/S301.csv", "extenbook_xlsx": "Technical/extenbooks/S301_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S301-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S301_extenbook.xlsx
+++ b/extenbooks/S301_extenbook.xlsx
@@ -4353,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A146"/>
+  <dimension ref="A1:A152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4392,7 +4392,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S301_research.json`</t>
+          <t>- Series research notes: `Technical/research/S301_research.json`</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -4566,178 +4566,178 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; it is very plausible that the minimum level of necessaries, which is always socially defined (Trigg 2004), rises as real income (y/p1) rises but not as fast as income, so that it declines as a share of income. [...] In other words, the Engel curve for necessary goods will exhibit saturation.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 93 &lt;!-- kb: ch03, p.93 (ch03_micro_foundations.md, saturation of the Engel curve) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>| **S301-A** | n/a (theoretical) | Shaikh 2016 eqs (3.4)-(3.11), p. 91-93; Figure 3.3 axis bounds p. 94 | dimensionless | analytic regeneration from equations |</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>## 3. Sources</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>The single subseries S301-A is an analytic curve. There is no "data" in the sense of historical observations; the data are the values of d(p1*x1)/dy evaluated on a discrete income grid in the same range as Shaikh's Figure 3.3 (y in [0, 60]).</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>| **S301-A** | n/a (theoretical) | Shaikh 2016 eqs (3.4)-(3.11), p. 91-93; Figure 3.3 axis bounds p. 94 | dimensionless | analytic regeneration from equations |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>S301 is **formula**-classified. The recipe:</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>The dataset's single data column (labelled S301-A) is an analytic curve. There is no "data" in the sense of historical observations; the data are the values of d(p1*x1)/dy evaluated on a discrete income grid in the same range as Shaikh's Figure 3.3 (y in [0, 60]).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1. Define an income grid: y in [0, 60], 121 points (step 0.5).</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2. Choose a calibration for x1min(y) under Case I (sub-linear). The book does not state Shaikh's exact calibration; we use the simplest functional form that matches the printed axis bounds:</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   `x1min(y) = alpha * y^beta` with `alpha = 1.0, beta = 0.5` (square-root path, monotone, elasticity 0.5).</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3. Choose c = 0.5 (mid-range; consistent with the Table 3.1 calibration for S308/S309 which uses pi=0.50).</t>
+          <t>S301 is **formula**-classified. The recipe:</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>4. Evaluate d(p1*x1)/dy = (1 - c) * d(p1*x1min)/dy + c = (1 - 0.5) * 0.5 * y^(-0.5) + 0.5 = 0.5 + 0.25 / sqrt(y) at each y (with p1 = 1, so p1*x1min = x1min).</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5. At y=0 the derivative is undefined (square-root singularity); we trim the curve to y in (0, 60] and report the asymptotic value at y=epsilon for completeness.</t>
+          <t>1. Define an income grid: y in [0, 60], 121 points (step 0.5).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2. Choose a calibration for x1min(y) under Case I (sub-linear). The book does not state Shaikh's exact calibration; we use the simplest functional form that matches the printed axis bounds:</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>**Formula**:</t>
+          <t xml:space="preserve">   `x1min(y) = alpha * y^beta` with `alpha = 1.0, beta = 0.5` (square-root path, monotone, elasticity 0.5).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>3. Choose c = 0.5 (mid-range; consistent with the Table 3.1 calibration for S308/S309 which uses pi=0.50).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>d(p1*x1)/dy = (1 - c) * d(x1min)/dy + c</t>
+          <t>4. Evaluate d(p1*x1)/dy = (1 - c) * d(p1*x1min)/dy + c = (1 - 0.5) * 0.5 * y^(-0.5) + 0.5 = 0.5 + 0.25 / sqrt(y) at each y (with p1 = 1, so p1*x1min = x1min).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">            = (1 - 0.5) * 0.5 * y^(-0.5) + 0.5         (with c=0.5, x1min = y^0.5)</t>
+          <t>5. At y=0 the derivative is undefined (square-root singularity); we trim the curve to y in (0, 60] and report the asymptotic value at y=epsilon for completeness.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            = 0.5 + 0.25 * y^(-0.5)</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>**Formula**:</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>```</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>At y=4: 0.5 + 0.25/2 = 0.625. At y=60: 0.5 + 0.25/sqrt(60) approx 0.532. The curve declines monotonically toward c=0.5 — consistent with Fig 3.3's apparent y-range of [0, ~0.8] and the qualitative saturation pattern Shaikh draws.</t>
+          <t>d(p1*x1)/dy = (1 - c) * d(x1min)/dy + c</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            = (1 - 0.5) * 0.5 * y^(-0.5) + 0.5         (with c=0.5, x1min = y^0.5)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t xml:space="preserve">            = 0.5 + 0.25 * y^(-0.5)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>- **No year dimension**. The abscissa is a synthetic income grid (model units 0-60).</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- The chopped CSV uses `year` as a per-row index column with the value `1` (point sequence number) for the theoretical grid — the `year` field is preserved for pipeline compatibility, but should not be interpreted as a calendar year. Refer to the `x_value` column (added for theoretical series) for the income value.</t>
+          <t>At y=4: 0.5 + 0.25/2 = 0.625. At y=60: 0.5 + 0.25/sqrt(60) approx 0.532. The curve declines monotonically toward c=0.5 — consistent with Fig 3.3's apparent y-range of [0, ~0.8] and the qualitative saturation pattern Shaikh draws.</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
@@ -4757,62 +4757,58 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>- **Output**: marginal expenditure share, dimensionless ratio.</t>
+          <t>- **No year dimension**. The abscissa is a synthetic income grid (model units 0-60).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- **x-axis**: income y in model units (0-60).</t>
+          <t>- The chopped CSV uses `year` as a per-row index column with the value `1` (point sequence number) for the theoretical grid — the `year` field is preserved for pipeline compatibility, but should not be interpreted as a calendar year. Refer to the `x_value` column (added for theoretical series) for the income value.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>- Every chopped CSV row carries `units = "marginal_share_dimensionless"`.</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- **Output**: marginal expenditure share, dimensionless ratio.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1. **Parameter calibration not stated by Shaikh.** The text states only the qualitative property (x1min sub-linear) and the axis ranges. We use square-root x1min(y) and c=0.5 as the simplest analytically-defensible choice consistent with the axis range. This is disclosed here and again in the EPR. The qualitative shape (declining marginal share toward c) is robust to the precise sub-linear form; the level at any given y is not.</t>
+          <t>- **x-axis**: income y in model units (0-60).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2. **No empirical content.** This is a pedagogical curve, not a measurement. There is no Allen &amp; Bowley table behind Fig 3.3 — that is the role of Figs 3.8/3.9 (S306/S307).</t>
+          <t>- Every chopped CSV row carries `units = "marginal_share_dimensionless"`.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>3. **Singularity at y=0.** The square-root choice has an infinite derivative at the origin. We trim to y in (0, 60] and report the curve from y=0.5 onward.</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4. **No proxy substitution; no synthetic gap-filling.** This series is by definition a closed-form evaluation of a published equation; the only judgement call is calibration, which is disclosed.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -4822,167 +4818,175 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>1. **Parameter calibration not stated by Shaikh.** The text states only the qualitative property (x1min sub-linear) and the axis ranges. We use square-root x1min(y) and c=0.5 as the simplest analytically-defensible choice consistent with the axis range. This is disclosed here and again in the EPR. The qualitative shape (declining marginal share toward c) is robust to the precise sub-linear form; the level at any given y is not.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2. **No empirical content.** This is a pedagogical curve, not a measurement. There is no Allen &amp; Bowley table behind Fig 3.3 — that is the role of Figs 3.8/3.9 (S306/S307).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none (this series has no predecessor in CD1 or CD2 — it was first ingested in RSCD).</t>
+          <t>3. **Singularity at y=0.** The square-root choice has an infinite derivative at the origin. We trim to y in (0, 60] and report the curve from y=0.5 onward.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>- **Companion analytic series**: S302 (Fig 3.4, share form), S303 (Fig 3.5, integrated Engel curve), all under the same Case I calibration.</t>
+          <t>4. **No proxy substitution; no synthetic gap-filling.** This series is by definition a closed-form evaluation of a published equation; the only judgement call is calibration, which is disclosed.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>- **Empirical counterpart**: S306 / S307 (the same conceptual object measured in 1904 working-class budgets).</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, p. 91-93 (text), p. 94 (Figure 3.3).</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.3 (documentation_type="theoretical", is_empirical=false).</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Companion analytic series**: S302 (Fig 3.4, share form), S303 (Fig 3.5, integrated Engel curve), all under the same Case I calibration.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>- **Empirical counterpart**: S306 / S307 (the same conceptual object measured in 1904 working-class budgets).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>- **Tolerance**: validator runs in `PASS_THEORETICAL` mode: it checks that (i) the curve is monotonically declining over y in [0.5, 60], (ii) the asymptote at y=60 is within [0.50, 0.55] (i.e., approaching c=0.5), (iii) all output values lie within the printed axis bound [0.0, 0.8].</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, p. 91-93 (text), p. 94 (Figure 3.3).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>- **Expected MAE** vs printed figure: not measured numerically. There are no published tabulated points to compare against. The validator returns `status=PASS_THEORETICAL` when shape and bound checks pass.</t>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.3 (documentation_type="theoretical", is_empirical=false).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>- **CD2 divergence**: not applicable (no CD2 predecessor).</t>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator runs in its theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values): it checks that (i) the curve is monotonically declining over y in [0.5, 60], (ii) the asymptote at y=60 is within [0.50, 0.55] (i.e., approaching c=0.5), (iii) all output values lie within the printed axis bound [0.0, 0.8].</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)** vs printed figure: not measured numerically. There are no published tabulated points to compare against. The validator passes in its theoretical-curve mode when shape and bound checks pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>- **Comparison with earlier reconstructions**: not applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4">
         <f>== EPR: S301_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t># S301 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>**Series**: S301 — Change in Expenditure on Necessaries Relative to Change in Income, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>**Extension classification**: `not_applicable_theoretical`</t>
-        </is>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t># S301 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>**Related**: `S301_DPR.md`, `Technical/research/S301_research.json`</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>**Series**: S301 — Change in Expenditure on Necessaries Relative to Change in Income, Case I</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Record type**: Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>**Content type**: `theoretical`</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Extension classification**: `not_applicable_theoretical`</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S301 is a `theoretical` series (per Phase 3 re-typing, ratified in `CH3_ADEQUACY_REPORT.json`). It is an analytic curve derived from Shaikh's equations (3.5)-(3.11) under Case I, plotted over a synthetic income grid. There is no time dimension.</t>
+          <t>**Related**: `S301_DPR.md`, `Technical/research/S301_research.json`</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4996,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5006,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. The series is regenerated from the published equations on every loader run. There is nothing to splice forward.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5016,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>S301 is a `theoretical` series (this classification was assigned during the data-intake review and ratified in `CH3_ADEQUACY_REPORT.json`). It is an analytic curve derived from Shaikh's equations (3.5)-(3.11) under Case I, plotted over a synthetic income grid. There is no time dimension.</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5026,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Not applicable. The "extension" of a theoretical curve is the curve itself — recomputed each run from the same equations and parameters. If Shaikh ever publishes additional Case I material (e.g., a Case I-bis with a different x1min(y) profile), this would constitute a *variant* of S301, not an *extension* — it would be authored as a new series or as a methodology variant under the Anu variant infrastructure.</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5036,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. The series is regenerated from the published equations each time the data-loading step runs. There is nothing to splice forward.</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>No proxy substitution. The "data" are Shaikh's own equations evaluated on the income grid. The only judgement call is the calibration of x1min(y) and c, which are documented in `S301_DPR.md` §4.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5056,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>Not applicable. The "extension" of a theoretical curve is the curve itself — recomputed each run from the same equations and parameters. If Shaikh ever publishes additional Case I material (e.g., a Case I-bis with a different x1min(y) profile), this would constitute a *variant* of S301, not an *extension* — it would be authored as a new series or as a methodology variant under the Anu variant infrastructure.</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5066,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>No synthetic data in the prohibited sense (anu-framework §No Synthetic Data). The curve values are the deterministic output of evaluating eq (3.5) at each grid point — this is the *documented analytical method* of the original source (Shaikh's own equations). Per the framework: "No approximations or interpolations unless they are the documented analytical method of the original source." Evaluating the published equation at grid points IS the documented method.</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5076,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>The income grid itself (y in (0, 60]) is an arbitrary discretisation; Shaikh's Figure 3.3 also presents the curve on a continuous axis without publishing a tabulated grid. Our 121-point grid is denser than the printed figure and chosen for chopped-CSV convenience; the curve at any specific y is exactly the analytic value, not an interpolant.</t>
+          <t>No proxy substitution. The "data" are Shaikh's own equations evaluated on the income grid. The only judgement call is the calibration of x1min(y) and c, which are documented in `S301_DPR.md` §4.</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5086,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>## 5. No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
@@ -5092,35 +5096,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>No synthetic data in the prohibited sense (anu-framework §No Synthetic Data). The curve values are the deterministic output of evaluating eq (3.5) at each grid point — this is the *documented analytical method* of the original source (Shaikh's own equations). Per the framework: "No approximations or interpolations unless they are the documented analytical method of the original source." Evaluating the published equation at grid points IS the documented method.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>| Calibration choice (x1min(y), c) departs from book's apparent figure | V03 shape/bounds checker flags out-of-range values | Re-calibrate; document new choice in DPR |</t>
+          <t>The income grid itself (y in (0, 60]) is an arbitrary discretisation; Shaikh's Figure 3.3 also presents the curve on a continuous axis without publishing a tabulated grid. Our 121-point grid is denser than the printed figure and chosen for chopped-CSV convenience; the curve at any specific y is exactly the analytic value, not an interpolant.</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>| Numeric overflow at y=0 (square-root singularity) | Loader filters y&lt;=0.5 | Trim grid to y in [0.5, 60]; documented as a known artefact |</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>| Disagreement with empirical analogs (S306/S307) | Out of scope for V03 of S301; tracked in chapter-level analysis (Phase 9) | Not a S301 failure — the theoretical claim is compatibility with shape, not exact agreement with the 1904 cross-section |</t>
+          <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
@@ -5130,27 +5126,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Not applicable. S301 has no CD2 predecessor (`predecessor_ids.cd2_id == null`). The chapter as a whole was not in the CD2 registry's S30* range. The V03 validator omits the CD2 comparison block for this series.</t>
+          <t>| Calibration choice (x1min(y), c) departs from book's apparent figure | The validation step's shape/bounds checker flags out-of-range values | Re-calibrate; document new choice in the Data Provenance Record (DPR) |</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>| Numeric overflow at y=0 (square-root singularity) | The data-loading step filters y&lt;=0.5 | Trim grid to y in [0.5, 60]; documented as a known artefact |</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>## 8. Why no API extension applies</t>
+          <t>| Disagreement with empirical analogs (S306/S307) | Out of scope for the validation step of S301; tracked in later chapter-level analysis | Not a S301 failure — the theoretical claim is compatibility with shape, not exact agreement with the 1904 cross-section |</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5164,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Theoretical curves are not extendable in the time-series sense. There is no agency or release schedule that "publishes new values" of a closed-form expression. The Anu Framework rule on extension applies only to `time_series` series.</t>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5174,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>This series will be re-evaluated on every loader run from the same equations — that is the only meaningful sense in which it is "kept current."</t>
+          <t>Not applicable. Predecessor series: none (first constructed in this dataset). S301 was not part of an earlier reconstruction of this project (internally called CD2); that earlier reconstruction did not contain this chapter's series. The validation step therefore omits the predecessor-comparison block for this series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Theoretical curves are not extendable in the time-series sense. There is no agency or release schedule that "publishes new values" of a closed-form expression. The Anu Framework rule on extension applies only to `time_series` series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>This series will be re-evaluated each time the data-loading step runs, from the same equations — that is the only meaningful sense in which it is "kept current."</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5396,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5531,7 +5565,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T22:01:40.917916+00:00</t>
+          <t>2026-07-02T06:22:02.966005+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S301_extenbook.xlsx
+++ b/extenbooks/S301_extenbook.xlsx
@@ -4406,7 +4406,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:02.966005+00:00</t>
+          <t>2026-07-11T03:44:24.646843+00:00</t>
         </is>
       </c>
     </row>
@@ -5592,11 +5592,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5619,6 +5619,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_EQ_3_4_3_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable analytic curve (Shaikh Fig 3.3): marginal expenditure share on the necessary good vs income, 119 clean points, monotone-declining toward c. Renders as an x-y curve (x = income grid in model units, carried in the 'year' index column, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S301/P02_S301 pipelines exist and replicate.py --series S301 builds the chopped (PASS). Caveat: levels depend on an agent-chosen calibration (x1min = y^0.5, c = 0.5) disclosed in the DPR \u00a77; only the qualitative shape is faithful to the book. KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.3.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S301_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S301_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Theoretical curve; no historical observations. Calibrated to match the printed axis bounds of the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>marginal expenditure share (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
